--- a/public/administrative-personnel-dashboard/personnel-management/FT-RH-09.xlsx
+++ b/public/administrative-personnel-dashboard/personnel-management/FT-RH-09.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LGress\Desktop\sicapsystem\public\administrative-personnel-dashboard\personnel-management\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D17C1C8C-7496-4F2C-90F1-40CFA407C4E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E98216B1-2449-4484-9018-AE908C83ACD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1125" yWindow="1125" windowWidth="21600" windowHeight="13845" xr2:uid="{659D26A7-1438-45CE-803F-CE796684F393}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{659D26A7-1438-45CE-803F-CE796684F393}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -511,9 +511,78 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -535,33 +604,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -569,51 +614,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1030,276 +1030,276 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5913A634-D9C4-461D-BC0F-4ED8E46DC927}">
   <dimension ref="A1:R34"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.140625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="11.42578125" style="2"/>
+    <col min="1" max="1" width="8.109375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="11.44140625" style="2"/>
     <col min="3" max="3" width="5" style="2" customWidth="1"/>
-    <col min="4" max="4" width="4.42578125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="9.140625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="4.44140625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="4.6640625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="9.109375" style="2" customWidth="1"/>
     <col min="7" max="7" width="5" style="2" customWidth="1"/>
-    <col min="8" max="10" width="4.42578125" style="2" customWidth="1"/>
-    <col min="11" max="11" width="3.85546875" style="2" customWidth="1"/>
-    <col min="12" max="12" width="3.42578125" style="2" customWidth="1"/>
-    <col min="13" max="14" width="4.42578125" style="2" customWidth="1"/>
+    <col min="8" max="10" width="4.44140625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="3.88671875" style="2" customWidth="1"/>
+    <col min="12" max="12" width="3.44140625" style="2" customWidth="1"/>
+    <col min="13" max="14" width="4.44140625" style="2" customWidth="1"/>
     <col min="15" max="15" width="6" style="2" customWidth="1"/>
     <col min="16" max="17" width="3" style="2" customWidth="1"/>
-    <col min="18" max="18" width="5.140625" style="2" customWidth="1"/>
-    <col min="19" max="16384" width="11.42578125" style="2"/>
+    <col min="18" max="18" width="5.109375" style="2" customWidth="1"/>
+    <col min="19" max="16384" width="11.44140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="28"/>
-      <c r="B1" s="28"/>
-      <c r="C1" s="29" t="s">
+    <row r="1" spans="1:18" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="38"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
-      <c r="I1" s="29"/>
-      <c r="J1" s="29"/>
-      <c r="K1" s="29"/>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="20" t="s">
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
+      <c r="I1" s="39"/>
+      <c r="J1" s="39"/>
+      <c r="K1" s="39"/>
+      <c r="L1" s="39"/>
+      <c r="M1" s="39"/>
+      <c r="N1" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="O1" s="20"/>
-      <c r="P1" s="20"/>
-      <c r="Q1" s="20"/>
-      <c r="R1" s="20"/>
-    </row>
-    <row r="2" spans="1:18" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="28"/>
-      <c r="B2" s="28"/>
-      <c r="C2" s="30" t="s">
+      <c r="O1" s="37"/>
+      <c r="P1" s="37"/>
+      <c r="Q1" s="37"/>
+      <c r="R1" s="37"/>
+    </row>
+    <row r="2" spans="1:18" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="38"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30" t="s">
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40" t="s">
         <v>29</v>
       </c>
-      <c r="H2" s="30"/>
-      <c r="I2" s="30"/>
-      <c r="J2" s="31" t="s">
+      <c r="H2" s="40"/>
+      <c r="I2" s="40"/>
+      <c r="J2" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="K2" s="32"/>
-      <c r="L2" s="33"/>
+      <c r="K2" s="42"/>
+      <c r="L2" s="43"/>
       <c r="M2" s="1">
         <v>2</v>
       </c>
-      <c r="N2" s="20" t="s">
+      <c r="N2" s="37" t="s">
         <v>25</v>
       </c>
-      <c r="O2" s="20"/>
-      <c r="P2" s="20"/>
-      <c r="Q2" s="20"/>
-      <c r="R2" s="20"/>
-    </row>
-    <row r="3" spans="1:18" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="28"/>
-      <c r="B3" s="28"/>
-      <c r="C3" s="30" t="s">
+      <c r="O2" s="37"/>
+      <c r="P2" s="37"/>
+      <c r="Q2" s="37"/>
+      <c r="R2" s="37"/>
+    </row>
+    <row r="3" spans="1:18" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="38"/>
+      <c r="B3" s="38"/>
+      <c r="C3" s="40" t="s">
         <v>28</v>
       </c>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="30"/>
-      <c r="H3" s="30"/>
-      <c r="I3" s="30"/>
-      <c r="J3" s="30"/>
-      <c r="K3" s="30"/>
-      <c r="L3" s="30"/>
-      <c r="M3" s="30"/>
-      <c r="N3" s="20" t="s">
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
+      <c r="G3" s="40"/>
+      <c r="H3" s="40"/>
+      <c r="I3" s="40"/>
+      <c r="J3" s="40"/>
+      <c r="K3" s="40"/>
+      <c r="L3" s="40"/>
+      <c r="M3" s="40"/>
+      <c r="N3" s="37" t="s">
         <v>26</v>
       </c>
-      <c r="O3" s="20"/>
-      <c r="P3" s="20"/>
-      <c r="Q3" s="20"/>
-      <c r="R3" s="20"/>
-    </row>
-    <row r="4" spans="1:18" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="O3" s="37"/>
+      <c r="P3" s="37"/>
+      <c r="Q3" s="37"/>
+      <c r="R3" s="37"/>
+    </row>
+    <row r="4" spans="1:18" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="5"/>
       <c r="R4" s="12"/>
     </row>
-    <row r="5" spans="1:18" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="5"/>
-      <c r="I5" s="34" t="s">
+      <c r="I5" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="J5" s="34"/>
-      <c r="K5" s="34"/>
-      <c r="L5" s="34"/>
-      <c r="M5" s="34"/>
-      <c r="N5" s="34"/>
-      <c r="O5" s="37"/>
-      <c r="P5" s="35"/>
-      <c r="Q5" s="36"/>
+      <c r="J5" s="51"/>
+      <c r="K5" s="51"/>
+      <c r="L5" s="51"/>
+      <c r="M5" s="51"/>
+      <c r="N5" s="51"/>
+      <c r="O5" s="52"/>
+      <c r="P5" s="23"/>
+      <c r="Q5" s="24"/>
       <c r="R5" s="12"/>
     </row>
-    <row r="6" spans="1:18" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="5"/>
       <c r="R6" s="12"/>
     </row>
-    <row r="7" spans="1:18" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="5"/>
-      <c r="I7" s="34" t="s">
+      <c r="I7" s="51" t="s">
         <v>22</v>
       </c>
-      <c r="J7" s="34"/>
-      <c r="K7" s="34"/>
-      <c r="L7" s="34"/>
-      <c r="M7" s="34"/>
-      <c r="N7" s="34"/>
-      <c r="O7" s="34"/>
-      <c r="P7" s="35"/>
-      <c r="Q7" s="36"/>
+      <c r="J7" s="51"/>
+      <c r="K7" s="51"/>
+      <c r="L7" s="51"/>
+      <c r="M7" s="51"/>
+      <c r="N7" s="51"/>
+      <c r="O7" s="51"/>
+      <c r="P7" s="23"/>
+      <c r="Q7" s="24"/>
       <c r="R7" s="12"/>
     </row>
-    <row r="8" spans="1:18" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="5"/>
       <c r="R8" s="12"/>
     </row>
-    <row r="9" spans="1:18" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="5"/>
-      <c r="F9" s="51" t="s">
+      <c r="F9" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="G9" s="51"/>
-      <c r="H9" s="51"/>
-      <c r="I9" s="46" t="s">
+      <c r="G9" s="30"/>
+      <c r="H9" s="30"/>
+      <c r="I9" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="J9" s="46"/>
-      <c r="K9" s="47"/>
+      <c r="J9" s="25"/>
+      <c r="K9" s="26"/>
       <c r="L9" s="17"/>
       <c r="N9" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="P9" s="35"/>
-      <c r="Q9" s="36"/>
+      <c r="P9" s="23"/>
+      <c r="Q9" s="24"/>
       <c r="R9" s="12"/>
     </row>
-    <row r="10" spans="1:18" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5"/>
       <c r="R10" s="12"/>
     </row>
-    <row r="11" spans="1:18" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5"/>
-      <c r="F11" s="34" t="s">
+      <c r="F11" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="G11" s="34"/>
-      <c r="H11" s="34"/>
+      <c r="G11" s="51"/>
+      <c r="H11" s="51"/>
       <c r="I11" s="16"/>
       <c r="J11" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="K11" s="42"/>
-      <c r="L11" s="42"/>
-      <c r="M11" s="42"/>
-      <c r="N11" s="42"/>
+      <c r="K11" s="35"/>
+      <c r="L11" s="35"/>
+      <c r="M11" s="35"/>
+      <c r="N11" s="35"/>
       <c r="O11" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="P11" s="42"/>
-      <c r="Q11" s="42"/>
+      <c r="P11" s="35"/>
+      <c r="Q11" s="35"/>
       <c r="R11" s="12"/>
     </row>
-    <row r="12" spans="1:18" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5"/>
       <c r="R12" s="12"/>
     </row>
-    <row r="13" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="49"/>
-      <c r="D13" s="49"/>
-      <c r="E13" s="49"/>
-      <c r="F13" s="49"/>
-      <c r="G13" s="49"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="28"/>
+      <c r="G13" s="28"/>
       <c r="I13" s="14" t="s">
         <v>19</v>
       </c>
       <c r="J13" s="14"/>
-      <c r="M13" s="40"/>
-      <c r="N13" s="40"/>
-      <c r="O13" s="40"/>
-      <c r="P13" s="40"/>
-      <c r="Q13" s="40"/>
-      <c r="R13" s="41"/>
-    </row>
-    <row r="14" spans="1:18" s="19" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="21" t="s">
+      <c r="M13" s="31"/>
+      <c r="N13" s="31"/>
+      <c r="O13" s="31"/>
+      <c r="P13" s="31"/>
+      <c r="Q13" s="31"/>
+      <c r="R13" s="32"/>
+    </row>
+    <row r="14" spans="1:18" s="19" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="22"/>
-      <c r="C14" s="50"/>
-      <c r="D14" s="50"/>
-      <c r="E14" s="50"/>
-      <c r="F14" s="50"/>
-      <c r="G14" s="50"/>
-      <c r="I14" s="22" t="s">
+      <c r="B14" s="45"/>
+      <c r="C14" s="29"/>
+      <c r="D14" s="29"/>
+      <c r="E14" s="29"/>
+      <c r="F14" s="29"/>
+      <c r="G14" s="29"/>
+      <c r="I14" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="J14" s="22"/>
-      <c r="K14" s="22"/>
-      <c r="L14" s="22"/>
-      <c r="M14" s="49"/>
-      <c r="N14" s="49"/>
-      <c r="O14" s="49"/>
-      <c r="P14" s="49"/>
-      <c r="Q14" s="49"/>
-      <c r="R14" s="52"/>
-    </row>
-    <row r="15" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J14" s="45"/>
+      <c r="K14" s="45"/>
+      <c r="L14" s="45"/>
+      <c r="M14" s="28"/>
+      <c r="N14" s="28"/>
+      <c r="O14" s="28"/>
+      <c r="P14" s="28"/>
+      <c r="Q14" s="28"/>
+      <c r="R14" s="33"/>
+    </row>
+    <row r="15" spans="1:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="C15" s="50"/>
-      <c r="D15" s="50"/>
-      <c r="E15" s="50"/>
-      <c r="F15" s="50"/>
-      <c r="G15" s="50"/>
+      <c r="C15" s="29"/>
+      <c r="D15" s="29"/>
+      <c r="E15" s="29"/>
+      <c r="F15" s="29"/>
+      <c r="G15" s="29"/>
       <c r="I15" s="14" t="s">
         <v>17</v>
       </c>
       <c r="J15" s="14"/>
-      <c r="M15" s="40"/>
-      <c r="N15" s="40"/>
-      <c r="O15" s="40"/>
-      <c r="P15" s="40"/>
-      <c r="Q15" s="40"/>
-      <c r="R15" s="41"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="M15" s="31"/>
+      <c r="N15" s="31"/>
+      <c r="O15" s="31"/>
+      <c r="P15" s="31"/>
+      <c r="Q15" s="31"/>
+      <c r="R15" s="32"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" s="5"/>
       <c r="I16" s="14" t="s">
         <v>16</v>
       </c>
       <c r="J16" s="14"/>
-      <c r="M16" s="40"/>
-      <c r="N16" s="40"/>
-      <c r="O16" s="40"/>
-      <c r="P16" s="40"/>
-      <c r="Q16" s="40"/>
-      <c r="R16" s="41"/>
-    </row>
-    <row r="17" spans="1:18" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M16" s="31"/>
+      <c r="N16" s="31"/>
+      <c r="O16" s="31"/>
+      <c r="P16" s="31"/>
+      <c r="Q16" s="31"/>
+      <c r="R16" s="32"/>
+    </row>
+    <row r="17" spans="1:18" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5"/>
       <c r="R17" s="12"/>
     </row>
-    <row r="18" spans="1:18" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="9" t="s">
         <v>0</v>
       </c>
@@ -1320,7 +1320,7 @@
       <c r="P18" s="3"/>
       <c r="R18" s="12"/>
     </row>
-    <row r="19" spans="1:18" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="8"/>
       <c r="B19" s="10" t="s">
         <v>1</v>
@@ -1333,22 +1333,22 @@
       </c>
       <c r="G19" s="18"/>
       <c r="H19" s="3"/>
-      <c r="I19" s="53" t="s">
+      <c r="I19" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="J19" s="53"/>
-      <c r="K19" s="54"/>
+      <c r="J19" s="34"/>
+      <c r="K19" s="36"/>
       <c r="L19" s="18"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="P19" s="38"/>
-      <c r="Q19" s="39"/>
+      <c r="P19" s="53"/>
+      <c r="Q19" s="54"/>
       <c r="R19" s="12"/>
     </row>
-    <row r="20" spans="1:18" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:18" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="8"/>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
@@ -1367,7 +1367,7 @@
       <c r="P20" s="3"/>
       <c r="R20" s="12"/>
     </row>
-    <row r="21" spans="1:18" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="8" t="s">
         <v>5</v>
       </c>
@@ -1388,30 +1388,30 @@
       <c r="P21" s="3"/>
       <c r="R21" s="12"/>
     </row>
-    <row r="22" spans="1:18" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="8"/>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
-      <c r="D22" s="53" t="s">
+      <c r="D22" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="E22" s="53"/>
-      <c r="F22" s="53"/>
+      <c r="E22" s="34"/>
+      <c r="F22" s="34"/>
       <c r="G22" s="18"/>
       <c r="H22" s="3"/>
-      <c r="I22" s="53" t="s">
+      <c r="I22" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="J22" s="53"/>
-      <c r="K22" s="53"/>
-      <c r="L22" s="54"/>
+      <c r="J22" s="34"/>
+      <c r="K22" s="34"/>
+      <c r="L22" s="36"/>
       <c r="M22" s="18"/>
       <c r="N22" s="3"/>
       <c r="O22" s="3"/>
       <c r="P22" s="3"/>
       <c r="R22" s="12"/>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" s="8"/>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
@@ -1430,151 +1430,151 @@
       <c r="P23" s="3"/>
       <c r="R23" s="12"/>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24" s="8" t="s">
         <v>8</v>
       </c>
       <c r="R24" s="12"/>
     </row>
-    <row r="25" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="48"/>
-      <c r="B25" s="48"/>
-      <c r="C25" s="48"/>
-      <c r="D25" s="48"/>
-      <c r="E25" s="48"/>
-      <c r="F25" s="48"/>
-      <c r="G25" s="48"/>
-      <c r="H25" s="48"/>
-      <c r="I25" s="48"/>
-      <c r="J25" s="48"/>
-      <c r="K25" s="48"/>
-      <c r="L25" s="48"/>
-      <c r="M25" s="48"/>
-      <c r="N25" s="48"/>
-      <c r="O25" s="48"/>
-      <c r="P25" s="48"/>
-      <c r="Q25" s="48"/>
-      <c r="R25" s="48"/>
-    </row>
-    <row r="26" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="48"/>
-      <c r="B26" s="48"/>
-      <c r="C26" s="48"/>
-      <c r="D26" s="48"/>
-      <c r="E26" s="48"/>
-      <c r="F26" s="48"/>
-      <c r="G26" s="48"/>
-      <c r="H26" s="48"/>
-      <c r="I26" s="48"/>
-      <c r="J26" s="48"/>
-      <c r="K26" s="48"/>
-      <c r="L26" s="48"/>
-      <c r="M26" s="48"/>
-      <c r="N26" s="48"/>
-      <c r="O26" s="48"/>
-      <c r="P26" s="48"/>
-      <c r="Q26" s="48"/>
-      <c r="R26" s="48"/>
-    </row>
-    <row r="27" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="48"/>
-      <c r="B27" s="48"/>
-      <c r="C27" s="48"/>
-      <c r="D27" s="48"/>
-      <c r="E27" s="48"/>
-      <c r="F27" s="48"/>
-      <c r="G27" s="48"/>
-      <c r="H27" s="48"/>
-      <c r="I27" s="48"/>
-      <c r="J27" s="48"/>
-      <c r="K27" s="48"/>
-      <c r="L27" s="48"/>
-      <c r="M27" s="48"/>
-      <c r="N27" s="48"/>
-      <c r="O27" s="48"/>
-      <c r="P27" s="48"/>
-      <c r="Q27" s="48"/>
-      <c r="R27" s="48"/>
-    </row>
-    <row r="28" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="48"/>
-      <c r="B28" s="48"/>
-      <c r="C28" s="48"/>
-      <c r="D28" s="48"/>
-      <c r="E28" s="48"/>
-      <c r="F28" s="48"/>
-      <c r="G28" s="48"/>
-      <c r="H28" s="48"/>
-      <c r="I28" s="48"/>
-      <c r="J28" s="48"/>
-      <c r="K28" s="48"/>
-      <c r="L28" s="48"/>
-      <c r="M28" s="48"/>
-      <c r="N28" s="48"/>
-      <c r="O28" s="48"/>
-      <c r="P28" s="48"/>
-      <c r="Q28" s="48"/>
-      <c r="R28" s="48"/>
-    </row>
-    <row r="29" spans="1:18" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="27"/>
+      <c r="B25" s="27"/>
+      <c r="C25" s="27"/>
+      <c r="D25" s="27"/>
+      <c r="E25" s="27"/>
+      <c r="F25" s="27"/>
+      <c r="G25" s="27"/>
+      <c r="H25" s="27"/>
+      <c r="I25" s="27"/>
+      <c r="J25" s="27"/>
+      <c r="K25" s="27"/>
+      <c r="L25" s="27"/>
+      <c r="M25" s="27"/>
+      <c r="N25" s="27"/>
+      <c r="O25" s="27"/>
+      <c r="P25" s="27"/>
+      <c r="Q25" s="27"/>
+      <c r="R25" s="27"/>
+    </row>
+    <row r="26" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="27"/>
+      <c r="B26" s="27"/>
+      <c r="C26" s="27"/>
+      <c r="D26" s="27"/>
+      <c r="E26" s="27"/>
+      <c r="F26" s="27"/>
+      <c r="G26" s="27"/>
+      <c r="H26" s="27"/>
+      <c r="I26" s="27"/>
+      <c r="J26" s="27"/>
+      <c r="K26" s="27"/>
+      <c r="L26" s="27"/>
+      <c r="M26" s="27"/>
+      <c r="N26" s="27"/>
+      <c r="O26" s="27"/>
+      <c r="P26" s="27"/>
+      <c r="Q26" s="27"/>
+      <c r="R26" s="27"/>
+    </row>
+    <row r="27" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="27"/>
+      <c r="B27" s="27"/>
+      <c r="C27" s="27"/>
+      <c r="D27" s="27"/>
+      <c r="E27" s="27"/>
+      <c r="F27" s="27"/>
+      <c r="G27" s="27"/>
+      <c r="H27" s="27"/>
+      <c r="I27" s="27"/>
+      <c r="J27" s="27"/>
+      <c r="K27" s="27"/>
+      <c r="L27" s="27"/>
+      <c r="M27" s="27"/>
+      <c r="N27" s="27"/>
+      <c r="O27" s="27"/>
+      <c r="P27" s="27"/>
+      <c r="Q27" s="27"/>
+      <c r="R27" s="27"/>
+    </row>
+    <row r="28" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="27"/>
+      <c r="B28" s="27"/>
+      <c r="C28" s="27"/>
+      <c r="D28" s="27"/>
+      <c r="E28" s="27"/>
+      <c r="F28" s="27"/>
+      <c r="G28" s="27"/>
+      <c r="H28" s="27"/>
+      <c r="I28" s="27"/>
+      <c r="J28" s="27"/>
+      <c r="K28" s="27"/>
+      <c r="L28" s="27"/>
+      <c r="M28" s="27"/>
+      <c r="N28" s="27"/>
+      <c r="O28" s="27"/>
+      <c r="P28" s="27"/>
+      <c r="Q28" s="27"/>
+      <c r="R28" s="27"/>
+    </row>
+    <row r="29" spans="1:18" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="5"/>
       <c r="R29" s="12"/>
     </row>
-    <row r="30" spans="1:18" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:18" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="5"/>
       <c r="R30" s="12"/>
     </row>
-    <row r="31" spans="1:18" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="23"/>
-      <c r="B31" s="24"/>
-      <c r="C31" s="24"/>
+    <row r="31" spans="1:18" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="46"/>
+      <c r="B31" s="47"/>
+      <c r="C31" s="47"/>
       <c r="R31" s="12"/>
     </row>
-    <row r="32" spans="1:18" s="19" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="27"/>
-      <c r="B32" s="25"/>
-      <c r="C32" s="25"/>
-      <c r="D32" s="25"/>
-      <c r="F32" s="25"/>
-      <c r="G32" s="25"/>
-      <c r="H32" s="25"/>
-      <c r="I32" s="25"/>
-      <c r="J32" s="25"/>
-      <c r="L32" s="25" t="s">
+    <row r="32" spans="1:18" s="19" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="50"/>
+      <c r="B32" s="48"/>
+      <c r="C32" s="48"/>
+      <c r="D32" s="48"/>
+      <c r="F32" s="48"/>
+      <c r="G32" s="48"/>
+      <c r="H32" s="48"/>
+      <c r="I32" s="48"/>
+      <c r="J32" s="48"/>
+      <c r="L32" s="48" t="s">
         <v>33</v>
       </c>
-      <c r="M32" s="25"/>
-      <c r="N32" s="25"/>
-      <c r="O32" s="25"/>
-      <c r="P32" s="25"/>
-      <c r="Q32" s="25"/>
-      <c r="R32" s="26"/>
-    </row>
-    <row r="33" spans="1:18" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="43" t="s">
+      <c r="M32" s="48"/>
+      <c r="N32" s="48"/>
+      <c r="O32" s="48"/>
+      <c r="P32" s="48"/>
+      <c r="Q32" s="48"/>
+      <c r="R32" s="49"/>
+    </row>
+    <row r="33" spans="1:18" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="B33" s="44"/>
-      <c r="C33" s="44"/>
-      <c r="D33" s="44"/>
-      <c r="F33" s="44" t="s">
+      <c r="B33" s="21"/>
+      <c r="C33" s="21"/>
+      <c r="D33" s="21"/>
+      <c r="F33" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="G33" s="44"/>
-      <c r="H33" s="44"/>
-      <c r="I33" s="44"/>
-      <c r="J33" s="44"/>
-      <c r="L33" s="44" t="s">
+      <c r="G33" s="21"/>
+      <c r="H33" s="21"/>
+      <c r="I33" s="21"/>
+      <c r="J33" s="21"/>
+      <c r="L33" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="M33" s="44"/>
-      <c r="N33" s="44"/>
-      <c r="O33" s="44"/>
-      <c r="P33" s="44"/>
-      <c r="Q33" s="44"/>
-      <c r="R33" s="45"/>
-    </row>
-    <row r="34" spans="1:18" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M33" s="21"/>
+      <c r="N33" s="21"/>
+      <c r="O33" s="21"/>
+      <c r="P33" s="21"/>
+      <c r="Q33" s="21"/>
+      <c r="R33" s="22"/>
+    </row>
+    <row r="34" spans="1:18" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="11" t="s">
         <v>32</v>
       </c>
@@ -1598,6 +1598,30 @@
     </row>
   </sheetData>
   <mergeCells count="40">
+    <mergeCell ref="F11:H11"/>
+    <mergeCell ref="K11:N11"/>
+    <mergeCell ref="I7:O7"/>
+    <mergeCell ref="P7:Q7"/>
+    <mergeCell ref="P5:Q5"/>
+    <mergeCell ref="I5:O5"/>
+    <mergeCell ref="P19:Q19"/>
+    <mergeCell ref="M15:R15"/>
+    <mergeCell ref="M16:R16"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="I14:L14"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="L32:R32"/>
+    <mergeCell ref="A32:D32"/>
+    <mergeCell ref="F32:J32"/>
+    <mergeCell ref="N1:R1"/>
+    <mergeCell ref="A1:B3"/>
+    <mergeCell ref="C1:M1"/>
+    <mergeCell ref="C3:M3"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="C2:F2"/>
+    <mergeCell ref="N2:R2"/>
+    <mergeCell ref="J2:L2"/>
+    <mergeCell ref="N3:R3"/>
     <mergeCell ref="A33:D33"/>
     <mergeCell ref="F33:J33"/>
     <mergeCell ref="L33:R33"/>
@@ -1614,30 +1638,6 @@
     <mergeCell ref="P11:Q11"/>
     <mergeCell ref="I19:K19"/>
     <mergeCell ref="I22:L22"/>
-    <mergeCell ref="N1:R1"/>
-    <mergeCell ref="A1:B3"/>
-    <mergeCell ref="C1:M1"/>
-    <mergeCell ref="C3:M3"/>
-    <mergeCell ref="G2:I2"/>
-    <mergeCell ref="C2:F2"/>
-    <mergeCell ref="N2:R2"/>
-    <mergeCell ref="J2:L2"/>
-    <mergeCell ref="N3:R3"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="I14:L14"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="L32:R32"/>
-    <mergeCell ref="A32:D32"/>
-    <mergeCell ref="F32:J32"/>
-    <mergeCell ref="I7:O7"/>
-    <mergeCell ref="P7:Q7"/>
-    <mergeCell ref="P5:Q5"/>
-    <mergeCell ref="I5:O5"/>
-    <mergeCell ref="P19:Q19"/>
-    <mergeCell ref="M15:R15"/>
-    <mergeCell ref="M16:R16"/>
-    <mergeCell ref="F11:H11"/>
-    <mergeCell ref="K11:N11"/>
   </mergeCells>
   <pageMargins left="0.27559055118110237" right="0.27559055118110237" top="0.11811023622047245" bottom="0.11811023622047245" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
